--- a/data/preparation/puma.xlsx
+++ b/data/preparation/puma.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q106"/>
+  <dimension ref="A1:P106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,12 +434,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Leadership_context</t>
+          <t>new_name</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Information_valence</t>
+          <t>Information_valence_human</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -489,15 +489,10 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>Coding_ambiguity</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
-        <is>
-          <t>Coding_ambiguity</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
         <is>
           <t>Alternative_context</t>
         </is>
@@ -506,7 +501,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JPN20P00-00</t>
+          <t>DEU20P00-00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -566,16 +561,13 @@
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>2020</v>
-      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JPN20P00-01</t>
+          <t>DEU20P00-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -635,16 +627,13 @@
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
-        <v>2020</v>
-      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JPN20P00-02</t>
+          <t>DEU20P00-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -704,16 +693,13 @@
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
-        <v>2020</v>
-      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JPN20P00-03</t>
+          <t>DEU20P00-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -773,16 +759,13 @@
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
-        <v>2020</v>
-      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JPN20P00-04</t>
+          <t>DEU20P00-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -842,16 +825,13 @@
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="n">
-        <v>2020</v>
-      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JPN20P00-05</t>
+          <t>DEU20P00-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -911,16 +891,13 @@
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="n">
-        <v>2020</v>
-      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JPN20P00-06</t>
+          <t>DEU20P00-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -980,16 +957,13 @@
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="n">
-        <v>2020</v>
-      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JPN20P00-07</t>
+          <t>DEU20P00-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1049,16 +1023,13 @@
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="n">
-        <v>2020</v>
-      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JPN20P00-08</t>
+          <t>DEU20P00-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1118,16 +1089,13 @@
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" t="n">
-        <v>2020</v>
-      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JPN20P00-09</t>
+          <t>DEU20P00-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1187,16 +1155,13 @@
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" t="n">
-        <v>2020</v>
-      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JPN20P00-10</t>
+          <t>DEU20P00-10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1256,16 +1221,13 @@
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="n">
-        <v>2020</v>
-      </c>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JPN20P00-11</t>
+          <t>DEU20P00-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1325,16 +1287,13 @@
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="n">
-        <v>2020</v>
-      </c>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JPN20P00-12</t>
+          <t>DEU20P00-12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1394,16 +1353,13 @@
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="n">
-        <v>2020</v>
-      </c>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JPN20P00-13</t>
+          <t>DEU20P00-13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1463,16 +1419,13 @@
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="n">
-        <v>2020</v>
-      </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JPN20P00-14</t>
+          <t>DEU20P00-14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1532,16 +1485,13 @@
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="n">
-        <v>2020</v>
-      </c>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JPN20P00-15</t>
+          <t>DEU20P00-15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1601,16 +1551,13 @@
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
-        <v>2020</v>
-      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JPN20P00-16</t>
+          <t>DEU20P00-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1670,16 +1617,13 @@
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
-      <c r="O18" t="n">
-        <v>2020</v>
-      </c>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JPN20P00-17</t>
+          <t>DEU20P00-17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1739,16 +1683,13 @@
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
-      <c r="O19" t="n">
-        <v>2020</v>
-      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>JPN20P00-18</t>
+          <t>DEU20P00-18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1810,11 +1751,8 @@
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
-      <c r="O20" t="n">
-        <v>2020</v>
-      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1879,11 +1817,8 @@
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
-      <c r="O21" t="n">
-        <v>2021</v>
-      </c>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1948,11 +1883,8 @@
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
-      <c r="O22" t="n">
-        <v>2021</v>
-      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2017,11 +1949,8 @@
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" t="n">
-        <v>2021</v>
-      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2086,11 +2015,8 @@
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
-        <v>2021</v>
-      </c>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2155,11 +2081,8 @@
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
-        <v>2021</v>
-      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2224,11 +2147,8 @@
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
-      <c r="O26" t="n">
-        <v>2021</v>
-      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2293,11 +2213,8 @@
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" t="n">
-        <v>2021</v>
-      </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2362,11 +2279,8 @@
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="n">
-        <v>2021</v>
-      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2431,11 +2345,8 @@
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
-      <c r="O29" t="n">
-        <v>2021</v>
-      </c>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2500,11 +2411,8 @@
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
-      <c r="O30" t="n">
-        <v>2021</v>
-      </c>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2569,11 +2477,8 @@
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" t="n">
-        <v>2021</v>
-      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2639,11 +2544,8 @@
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
-      <c r="O32" t="n">
-        <v>2021</v>
-      </c>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2708,11 +2610,8 @@
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
-      <c r="O33" t="n">
-        <v>2021</v>
-      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2777,11 +2676,8 @@
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="n">
-        <v>2021</v>
-      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2846,11 +2742,8 @@
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="n">
-        <v>2021</v>
-      </c>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2918,11 +2811,8 @@
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
-      <c r="O36" t="n">
-        <v>2021</v>
-      </c>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2987,11 +2877,8 @@
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
-      <c r="O37" t="n">
-        <v>2022</v>
-      </c>
+      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3056,11 +2943,8 @@
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
-      <c r="O38" t="n">
-        <v>2022</v>
-      </c>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3125,11 +3009,8 @@
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="n">
-        <v>2022</v>
-      </c>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3194,11 +3075,8 @@
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="n">
-        <v>2022</v>
-      </c>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3263,11 +3141,8 @@
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
-      <c r="O41" t="n">
-        <v>2022</v>
-      </c>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3332,11 +3207,8 @@
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
-      <c r="O42" t="n">
-        <v>2022</v>
-      </c>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3401,11 +3273,8 @@
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
-      <c r="O43" t="n">
-        <v>2022</v>
-      </c>
+      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3470,11 +3339,8 @@
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" t="n">
-        <v>2022</v>
-      </c>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3539,11 +3405,8 @@
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" t="n">
-        <v>2022</v>
-      </c>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3608,11 +3471,8 @@
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="n">
-        <v>2022</v>
-      </c>
+      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3677,11 +3537,8 @@
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="n">
-        <v>2022</v>
-      </c>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3746,11 +3603,8 @@
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" t="n">
-        <v>2022</v>
-      </c>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3815,11 +3669,8 @@
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" t="n">
-        <v>2022</v>
-      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3884,11 +3735,8 @@
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
-      <c r="O50" t="n">
-        <v>2022</v>
-      </c>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3953,11 +3801,8 @@
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="n">
-        <v>2022</v>
-      </c>
+      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4022,11 +3867,8 @@
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
-      <c r="O52" t="n">
-        <v>2022</v>
-      </c>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4091,11 +3933,8 @@
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
-      <c r="O53" t="n">
-        <v>2022</v>
-      </c>
+      <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4160,11 +3999,8 @@
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
-      <c r="O54" t="n">
-        <v>2022</v>
-      </c>
+      <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4229,11 +4065,8 @@
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
-      <c r="O55" t="n">
-        <v>2022</v>
-      </c>
+      <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4299,11 +4132,8 @@
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
-      <c r="O56" t="n">
-        <v>2022</v>
-      </c>
+      <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4368,11 +4198,8 @@
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
-      <c r="O57" t="n">
-        <v>2023</v>
-      </c>
+      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4437,11 +4264,8 @@
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
-      <c r="O58" t="n">
-        <v>2023</v>
-      </c>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4506,11 +4330,8 @@
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
-      <c r="O59" t="n">
-        <v>2023</v>
-      </c>
+      <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4576,11 +4397,8 @@
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
-      <c r="O60" t="n">
-        <v>2023</v>
-      </c>
+      <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4645,11 +4463,8 @@
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
-      <c r="O61" t="n">
-        <v>2023</v>
-      </c>
+      <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4714,11 +4529,8 @@
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
-      <c r="O62" t="n">
-        <v>2023</v>
-      </c>
+      <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4783,11 +4595,8 @@
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
-      <c r="O63" t="n">
-        <v>2023</v>
-      </c>
+      <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4852,11 +4661,8 @@
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
-      <c r="O64" t="n">
-        <v>2023</v>
-      </c>
+      <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4921,11 +4727,8 @@
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
-      <c r="O65" t="n">
-        <v>2023</v>
-      </c>
+      <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4990,11 +4793,8 @@
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
-      <c r="O66" t="n">
-        <v>2023</v>
-      </c>
+      <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5059,11 +4859,8 @@
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
-      <c r="O67" t="n">
-        <v>2023</v>
-      </c>
+      <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5128,11 +4925,8 @@
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
-      <c r="O68" t="n">
-        <v>2023</v>
-      </c>
+      <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5197,11 +4991,8 @@
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
-      <c r="O69" t="n">
-        <v>2023</v>
-      </c>
+      <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5266,11 +5057,8 @@
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
-      <c r="O70" t="n">
-        <v>2023</v>
-      </c>
+      <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5335,11 +5123,8 @@
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
-      <c r="O71" t="n">
-        <v>2023</v>
-      </c>
+      <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5404,11 +5189,8 @@
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
-      <c r="O72" t="n">
-        <v>2023</v>
-      </c>
+      <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5473,11 +5255,8 @@
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
-      <c r="O73" t="n">
-        <v>2023</v>
-      </c>
+      <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5542,11 +5321,8 @@
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
-      <c r="O74" t="n">
-        <v>2023</v>
-      </c>
+      <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5611,11 +5387,8 @@
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
-      <c r="O75" t="n">
-        <v>2023</v>
-      </c>
+      <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5680,11 +5453,8 @@
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
-      <c r="O76" t="n">
-        <v>2023</v>
-      </c>
+      <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5749,11 +5519,8 @@
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
-      <c r="O77" t="n">
-        <v>2023</v>
-      </c>
+      <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5818,11 +5585,8 @@
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
-      <c r="O78" t="n">
-        <v>2023</v>
-      </c>
+      <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5888,11 +5652,8 @@
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
-      <c r="O79" t="n">
-        <v>2023</v>
-      </c>
+      <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5957,11 +5718,8 @@
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
-      <c r="O80" t="n">
-        <v>2024</v>
-      </c>
+      <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6026,11 +5784,8 @@
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
-      <c r="O81" t="n">
-        <v>2024</v>
-      </c>
+      <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6095,11 +5850,8 @@
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
-      <c r="O82" t="n">
-        <v>2024</v>
-      </c>
+      <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6164,11 +5916,8 @@
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
-      <c r="O83" t="n">
-        <v>2024</v>
-      </c>
+      <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6233,11 +5982,8 @@
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
-      <c r="O84" t="n">
-        <v>2024</v>
-      </c>
+      <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6302,11 +6048,8 @@
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
-      <c r="O85" t="n">
-        <v>2024</v>
-      </c>
+      <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6371,11 +6114,8 @@
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
-      <c r="O86" t="n">
-        <v>2024</v>
-      </c>
+      <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6440,11 +6180,8 @@
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
-      <c r="O87" t="n">
-        <v>2024</v>
-      </c>
+      <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6509,11 +6246,8 @@
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
-      <c r="O88" t="n">
-        <v>2024</v>
-      </c>
+      <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6578,11 +6312,8 @@
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
-      <c r="O89" t="n">
-        <v>2024</v>
-      </c>
+      <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6648,11 +6379,8 @@
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
-      <c r="O90" t="n">
-        <v>2024</v>
-      </c>
+      <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6719,11 +6447,8 @@
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
-      <c r="O91" t="n">
-        <v>2025</v>
-      </c>
+      <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6790,11 +6515,8 @@
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
-      <c r="O92" t="n">
-        <v>2025</v>
-      </c>
+      <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6861,11 +6583,8 @@
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
-      <c r="O93" t="n">
-        <v>2025</v>
-      </c>
+      <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6932,11 +6651,8 @@
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
-      <c r="O94" t="n">
-        <v>2025</v>
-      </c>
+      <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7003,11 +6719,8 @@
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
-      <c r="O95" t="n">
-        <v>2025</v>
-      </c>
+      <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7074,11 +6787,8 @@
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
-      <c r="O96" t="n">
-        <v>2025</v>
-      </c>
+      <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7145,11 +6855,8 @@
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
-      <c r="O97" t="n">
-        <v>2025</v>
-      </c>
+      <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7216,11 +6923,8 @@
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
-      <c r="O98" t="n">
-        <v>2025</v>
-      </c>
+      <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7287,11 +6991,8 @@
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
-      <c r="O99" t="n">
-        <v>2025</v>
-      </c>
+      <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7358,11 +7059,8 @@
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
-      <c r="O100" t="n">
-        <v>2025</v>
-      </c>
+      <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7429,11 +7127,8 @@
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
-      <c r="O101" t="n">
-        <v>2025</v>
-      </c>
+      <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7500,11 +7195,8 @@
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
-      <c r="O102" t="n">
-        <v>2025</v>
-      </c>
+      <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7571,11 +7263,8 @@
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
-      <c r="O103" t="n">
-        <v>2025</v>
-      </c>
+      <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7642,11 +7331,8 @@
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
-      <c r="O104" t="n">
-        <v>2025</v>
-      </c>
+      <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7713,11 +7399,8 @@
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
-      <c r="O105" t="n">
-        <v>2025</v>
-      </c>
+      <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7785,11 +7468,8 @@
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
-      <c r="O106" t="n">
-        <v>2025</v>
-      </c>
+      <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
